--- a/SGC-CKN/Excel/bad36d3c-4832-49c8-96f1-d8ab1c064498_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-56_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/bad36d3c-4832-49c8-96f1-d8ab1c064498_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-56_D800_04-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t xml:space="preserve">18:02
+    <t xml:space="preserve">18:00
 03/04/2026</t>
   </si>
   <si>
@@ -145,7 +145,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">22:11
+    <t xml:space="preserve">22:00
 03/04/2026</t>
   </si>
   <si>
@@ -155,7 +155,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">23:11
+    <t xml:space="preserve">23:10
 03/04/2026</t>
   </si>
   <si>
@@ -176,10 +176,6 @@
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02:38
-04/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:52
@@ -1161,13 +1157,13 @@
         <v>-2</v>
       </c>
       <c r="H11" s="5">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="I11" s="5">
         <v>2</v>
       </c>
       <c r="J11" s="8">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1298,16 +1294,16 @@
         <v>-12.7</v>
       </c>
       <c r="G15" s="19">
-        <v>-21.1</v>
+        <v>-20.9</v>
       </c>
       <c r="H15" s="19">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="19">
-        <v>8.4</v>
-      </c>
-      <c r="J15" s="15">
-        <v>4.99</v>
+        <v>8.2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>5.47</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1330,19 +1326,19 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
-        <v>-21.1</v>
+        <v>-20.9</v>
       </c>
       <c r="G16" s="22">
         <v>-26.2</v>
       </c>
       <c r="H16" s="22">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="I16" s="22">
-        <v>5.1</v>
-      </c>
-      <c r="J16" s="8">
-        <v>5.1</v>
+        <v>5.3</v>
+      </c>
+      <c r="J16" s="15">
+        <v>4.54</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1371,13 +1367,13 @@
         <v>-39.5</v>
       </c>
       <c r="H17" s="25">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I17" s="25">
         <v>13.3</v>
       </c>
       <c r="J17" s="15">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1394,10 +1390,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>52</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>53</v>
       </c>
       <c r="F18" s="28">
         <v>-39.5</v>
@@ -1406,21 +1402,21 @@
         <v>-44.62</v>
       </c>
       <c r="H18" s="28">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="I18" s="28">
         <v>5.12</v>
       </c>
       <c r="J18" s="15">
-        <v>4.15</v>
+        <v>2.69</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1526,31 +1522,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1573,13 +1569,13 @@
         <v>-2</v>
       </c>
       <c r="G2" s="5">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H2" s="5">
         <v>2</v>
       </c>
       <c r="I2" s="8">
-        <v>6.67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1686,16 +1682,16 @@
         <v>-12.7</v>
       </c>
       <c r="F6" s="19">
-        <v>-21.1</v>
+        <v>-20.9</v>
       </c>
       <c r="G6" s="19">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="19">
-        <v>8.4</v>
-      </c>
-      <c r="I6" s="15">
-        <v>4.99</v>
+        <v>8.2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>5.47</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1712,19 +1708,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-21.1</v>
+        <v>-20.9</v>
       </c>
       <c r="F7" s="22">
         <v>-26.2</v>
       </c>
       <c r="G7" s="22">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="H7" s="22">
-        <v>5.1</v>
-      </c>
-      <c r="I7" s="8">
-        <v>5.1</v>
+        <v>5.3</v>
+      </c>
+      <c r="I7" s="15">
+        <v>4.54</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,13 +1743,13 @@
         <v>-39.5</v>
       </c>
       <c r="G8" s="25">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H8" s="25">
         <v>13.3</v>
       </c>
       <c r="I8" s="15">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1776,18 +1772,18 @@
         <v>-44.62</v>
       </c>
       <c r="G9" s="28">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="H9" s="28">
         <v>5.12</v>
       </c>
       <c r="I9" s="15">
-        <v>4.15</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1805,13 +1801,13 @@
         <v>-44.62</v>
       </c>
       <c r="G10" s="33">
-        <v>9.17</v>
+        <v>9.87</v>
       </c>
       <c r="H10" s="33">
         <v>44.62</v>
       </c>
       <c r="I10" s="33">
-        <v>4.87</v>
+        <v>4.52</v>
       </c>
     </row>
   </sheetData>
